--- a/auto_vlm/input_cases.xlsx
+++ b/auto_vlm/input_cases.xlsx
@@ -1,127 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Byeongjin Jeong\codex\auto_vlm\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0CCAF2-8D3D-4230-ABD3-FF93F5732DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41240" yWindow="2840" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="41240" yWindow="2840" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cases" sheetId="1" r:id="rId1"/>
-    <sheet name="feature_options" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feature_options" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
-  <si>
-    <t>case_id</t>
-  </si>
-  <si>
-    <t>qv_video_path</t>
-  </si>
-  <si>
-    <t>raw_video_path</t>
-  </si>
-  <si>
-    <t>frame_list</t>
-  </si>
-  <si>
-    <t>sampling_frame</t>
-  </si>
-  <si>
-    <t>json_dir</t>
-  </si>
-  <si>
-    <t>focus_feature</t>
-  </si>
-  <si>
-    <t>CASE_001</t>
-  </si>
-  <si>
-    <t>test_video\AshLey_TN18TC_20260425_135904_0006\AshLey_TN18TC_20260425_135904_0006.mp4</t>
-  </si>
-  <si>
-    <t>test_video\AshLey_TN18TC_20260425_135904_0006.h264</t>
-  </si>
-  <si>
-    <t>test_video\AshLey_TN18TC_20260425_135904_0006\SV_INSPECTOR_json</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>CASE_002</t>
-  </si>
-  <si>
-    <t>test_video\AshLey_TN18TC_20260425_135904_0007\AshLey_TN18TC_20260425_135904_0007.mp4</t>
-  </si>
-  <si>
-    <t>test_video\AshLey_TN18TC_20260425_135904_0007.h264</t>
-  </si>
-  <si>
-    <t>153,235</t>
-  </si>
-  <si>
-    <t>test_video\AshLey_TN18TC_20260425_135904_0007\SV_INSPECTOR_json</t>
-  </si>
-  <si>
-    <t>OD</t>
-  </si>
-  <si>
-    <t>LD</t>
-  </si>
-  <si>
-    <t>RBD</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>TL</t>
-  </si>
-  <si>
-    <t>520</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B9BD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -129,27 +91,125 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -437,126 +497,1162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="72" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="65" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" style="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>qv_video_path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>raw_video_path</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>frame_list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sampling_frame</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>json_dir</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>focus_feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CASE_001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>test_video\AshLey_TN18TC_20260425_135904_0006\AshLey_TN18TC_20260425_135904_0006.mp4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>test_video\AshLey_TN18TC_20260425_135904_0006.h264</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>test_video\AshLey_TN18TC_20260425_135904_0006\SV_INSPECTOR_json</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test_video\AshLey_TN18TC_20260425_135904_0007\AshLey_TN18TC_20260425_135904_0007.mp4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>test_video\AshLey_TN18TC_20260425_135904_0007.h264</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>153,235</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>test_video\AshLey_TN18TC_20260425_135904_0007\SV_INSPECTOR_json</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Auto VLM input_cases.xlsx 사용자 가이드</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>핵심 규칙</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>cases 시트의 1행 header는 변경하지 마세요. 실제 입력은 2행부터 작성합니다.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>필수 입력</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>case_id + qv_video_path 또는 video_path 중 하나가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>프레임 선택</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>frame_list와 sampling_frame은 둘 중 하나만 입력합니다. 둘 다 입력하거나 둘 다 비우면 오류입니다.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>feature 선택</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>focus_feature는 ALL, OD, LD, RBD, TS, TL 또는 OD,RBD처럼 쉼표로 여러 개 입력할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>경로 입력</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>상대경로는 실행 위치 기준입니다. 현재 파일 예시는 test_video\... 형태를 사용합니다.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>focus_feature 허용값</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>의미</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>OD, LD, RBD, TS, TL 전체 리뷰</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>기본값. 빈칸도 ALL로 처리됩니다.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Object Detection 리뷰</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>객체 검출 feature만 테스트합니다.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Lane Detection 리뷰</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>차선 feature만 테스트합니다.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RBD</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Road Boundary Detection 리뷰</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>도로 경계 feature만 테스트합니다.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Traffic Sign 리뷰</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>교통 표지판 feature만 테스트합니다.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Traffic Light 리뷰</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>신호등 feature만 테스트합니다.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>OD,RBD</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>여러 feature 조합 리뷰</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>쉼표로 구분합니다. ALL과 개별 feature를 함께 쓰지 마세요.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>cases 시트 현재 컬럼</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>컬럼명</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>필수 여부</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>입력 예시</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>주의사항</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>파서 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>CASE_001</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>케이스 식별자입니다. 결과 package_id와 report row의 기준이 됩니다.</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>비워두면 오류입니다.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>앞뒤 공백 제거 후 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>qv_video_path</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>필수*</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>test_video\...\sample.mp4</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Qualification Visualizer overlay 영상 경로입니다.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>video_path 컬럼을 대신 쓸 수도 있지만 현재 workbook은 qv_video_path를 사용합니다.</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>video_path 입력값으로도 함께 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>raw_video_path</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>test_video\...\sample.h264</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>원본 raw 영상 경로입니다.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>없으면 raw frame evidence가 제한됩니다.</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>있으면 raw frame 추출</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>frame_list</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>조건부 필수</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>520 또는 153,235</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>리뷰할 정확한 frame 번호 목록입니다.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>sampling_frame과 동시에 쓰면 오류입니다.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>쉼표 분리 후 정수 목록으로 변환</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>sampling_frame</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>조건부 필수</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>전체 영상에서 일정 간격으로 sampling할 때 사용합니다.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>frame_list가 있으면 비워두세요.</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>양의 정수로 변환</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>json_dir</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>test_video\...\SV_INSPECTOR_json</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>frame별 JSON 파일 폴더입니다.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>없으면 JSON evidence가 unavailable로 기록됩니다.</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>sampled frame과 같은 00000123.json 탐색</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>focus_feature</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>ALL 또는 OD,RBD</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>리뷰할 feature를 선택합니다.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ALL과 OD 같은 개별 feature를 섞지 마세요. 예: ALL,OD 금지</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>빈칸은 ALL, 쉼표 조합 허용</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>필요할 때 추가 가능한 지원 컬럼</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>컬럼명</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>필수 여부</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>입력 예시</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>주의사항</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>파서 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>video_path</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>qv_video_path 대체</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>test_video\...\sample.mp4</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>qv_video_path가 없을 때 QV/overlay 영상 경로로 사용됩니다.</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>qv_video_path와 둘 다 있으면 qv_video_path가 우선입니다.</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>qv_video_path fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>sample_count</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>sampling_frame 대체</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>구형 이름입니다. sampling_frame이 비어 있을 때만 사용됩니다.</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>새 파일에서는 sampling_frame 사용을 권장합니다.</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>sampling_frame fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>project_type</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>APTIV_FVC</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>프로젝트/고객 타입 메타데이터입니다.</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>비워도 실행은 가능합니다.</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>package metadata에 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>start_frame</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>sampling_frame 방식에서 sampling 시작 frame을 제한합니다.</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>frame_list와 같이 쓰는 경우 의미가 제한적입니다.</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>정수로 변환</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>end_frame</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>sampling_frame 방식에서 sampling 종료 frame을 제한합니다.</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>start_frame보다 작으면 오류입니다.</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>정수로 변환</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>lidar_overlay_path</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>path\lidar_overlay.mp4</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>GT/reference overlay 경로입니다.</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>현재 gtless workflow에서는 없을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>metadata에 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>lidar_json_dir</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>path\lidar_json</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>LiDAR/reference JSON 폴더입니다.</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>필요한 workflow에서만 입력합니다.</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>metadata에 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>lidar_json_path</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>path\frame.json</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>단일 LiDAR/reference JSON 파일입니다.</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>lidar_json_dir와 중복 의미가 될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>metadata에 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>frame_metadata</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>weather=rain;scene=urban</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>frame 단위 부가 메타데이터입니다.</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>세미콜론으로 key=value를 구분합니다.</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>dict로 변환</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>memo</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>사용자 메모입니다.</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>판정 정답으로 사용하지 않습니다.</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>metadata/report 보조 정보</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A20:F20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>